--- a/site/ADP-Workforce-Now-to-Okta-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-Okta-Integration-Guide/headings.xlsx
@@ -1013,66 +1013,66 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Correlation for Existing Users in Okta</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K5VEYCS797A06QXKZWJXFDJY</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Okta-Integration-Guide/#h_01K5VEYCS797A06QXKZWJXFDJY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Okta-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Mapping Custom Attributes</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01K7H3FBM0V1D99VEW60RCKMFX</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Okta-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Okta-Integration-Guide/#h_01K7H3FBM0V1D99VEW60RCKMFX</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mapping Custom Attributes</t>
+          <t>Group Rules</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K7H3FBM0V1D99VEW60RCKMFX</t>
+          <t>h_01KJ53Y3H4BWX0QQW00JSQW5WC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Okta-Integration-Guide/#h_01K7H3FBM0V1D99VEW60RCKMFX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Okta-Integration-Guide/#h_01KJ53Y3H4BWX0QQW00JSQW5WC</t>
         </is>
       </c>
     </row>
